--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/_adv.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/_adv.xlsx
@@ -970,8 +970,8 @@
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>Você se aproximou do altar, revivendo a história dos deuses em seus pensamentos.
-■Fé 《#god_name》
+          <t>- Você caminha até o altar, revivendo em silêncio o saber dos deuses. 
+ &lt;color=olive&gt;《#god_name》&lt;/color&gt;
 #god_desc
 #god_benefit</t>
         </is>
@@ -1247,9 +1247,9 @@
           <t>Worship #god_name.</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>Adorar #god_name</t>
+          <t>Cultuar #god_name.</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
           <t>(Leave)</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" s="8" t="inlineStr">
         <is>
           <t>(Sair)</t>
         </is>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Uma voz divina ecoa em sua mente.
+          <t>Uma voz divina ecoa na sua cabeça.
 "#godtalk_worship"</t>
         </is>
       </c>
@@ -24508,7 +24508,7 @@
           <t>Marriage</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>Casamento</t>
         </is>
@@ -25094,7 +25094,7 @@
       <c r="K16" s="8" t="inlineStr">
         <is>
           <t>No #2 do Ano Sierra #1, #4 pediu #5 em casamento em #3.
-Os dois ficaram em silêncio, de mãos dadas, e prometeram que seu amor duraria para sempre.</t>
+Os dois ficaram em silêncio, de mãos entrelaçadas, e prometeram um amor para durar para sempre.</t>
         </is>
       </c>
       <c r="L16" s="8" t="n"/>
@@ -25373,7 +25373,7 @@
           <t>Without you, life has no meaning.</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" s="8" t="inlineStr">
         <is>
           <t>Sem você, a vida não tem sentido.</t>
         </is>
@@ -25535,11 +25535,11 @@
 When the moonlight spills down upon the earth, under an eternal vow, the two shall be firmly bound as one.</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>Ó estrelas insones, ó lua que gira sem fim. Nesta noite, vigiem a partida destes dois e abençoem este dia afortunado.
-Que o buquê oferecido ao céu noturno, e o beijo trocado pelo amanhã, um dia deem frutos em um tempo que brilha como ouro.
-Quando o luar se derrama sobre a terra, sob um voto eterno, os dois serão firmemente unidos como um só.</t>
+          <t>O estrelas insones, ó lua de voltas eternas. Nesta noite, vigiem a partida destes dois e abençoem este dia ditoso.
+Que o buquê ofertado ao céu noturno, e o beijo trocado pelo amanhã, um dia dêem fruto num tempo que brilha como ouro.
+Quando o luar se derramar sobre a terra, sob um voto eterno, os dois serão firmemente atados em um.</t>
         </is>
       </c>
     </row>
@@ -25576,10 +25576,10 @@
 Do you swear to take #tg as your lifelong partner, to never let go of #tg_his hand in joyful mornings or tearful nights, and to remain by #tg_his side forever?</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K36" s="8" t="inlineStr">
         <is>
           <t>#pc_full.
-Você jura aceitar #tg como seu parceiro(a) para toda a vida, nunca soltar a mão de #tg_his em manhãs alegres ou noites de lágrimas, e permanecer ao lado de #tg_his para sempre?</t>
+Jura tomar #tg como parceiro(a) de sua vida, nunca soltar a mão de #tg_his em manhãs alegres ou noites de lágrimas, e permanecer ao lado de #tg para sempre?</t>
         </is>
       </c>
     </row>
@@ -25607,7 +25607,7 @@
           <t>Yes.</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K37" s="8" t="inlineStr">
         <is>
           <t>Sim.</t>
         </is>
@@ -25637,7 +25637,7 @@
           <t>No.</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K38" s="8" t="inlineStr">
         <is>
           <t>Não.</t>
         </is>
@@ -25664,7 +25664,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K42" s="8" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -25739,10 +25739,10 @@
 Do you swear to take #pc_full as your one and only partner, to entrust your heart through storms of fate and in peaceful slumber, and to walk together always?</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K51" s="8" t="inlineStr">
         <is>
           <t>#tg.
-Você jura aceitar #pc_full como seu único e verdadeiro parceiro(a), confiar seu coração através das tempestades do destino e nos momentos de paz, e caminhar sempre juntos?</t>
+Jura tomar #pc_full como seu único par, confiar seu coração nas tempestades do destino e no sono em paz, e caminhar juntos sempre?</t>
         </is>
       </c>
     </row>
@@ -25772,9 +25772,9 @@
           <t>...Yes, I do.</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K53" s="8" t="inlineStr">
         <is>
-          <t>...Sim, eu aceito.</t>
+          <t>...Sim, juro.</t>
         </is>
       </c>
     </row>
@@ -25811,10 +25811,10 @@
 Now... the kiss of your vow.</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K55" s="8" t="inlineStr">
         <is>
-          <t>Diante da testemunha das estrelas, estes dois estão agora unidos como um só. Que a deusa da fortuna os abençoe!
-Agora... o beijo de seu voto.</t>
+          <t>Diante do testemunho das estrelas, estes dois agora se unem em um. Que a deusa da sorte abençoe os dois!
+Agora... o beijo do voto.</t>
         </is>
       </c>
     </row>
@@ -25842,7 +25842,7 @@
           <t>(Kiss #tg_him)</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="K56" s="8" t="inlineStr">
         <is>
           <t>(Beijar #tg_him)</t>
         </is>
@@ -25872,9 +25872,9 @@
           <t>(Make love with #tg_him)</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="K57" s="8" t="inlineStr">
         <is>
-          <t>(Fazer amor com #tg_him)</t>
+          <t>(Amar #tg_him)</t>
         </is>
       </c>
     </row>
@@ -25902,9 +25902,9 @@
           <t>(Blush and stay silent)</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="K58" s="8" t="inlineStr">
         <is>
-          <t>(Corar e ficar em silêncio)</t>
+          <t>(Corar e ficar calado)</t>
         </is>
       </c>
     </row>
@@ -25932,7 +25932,7 @@
           <t>(Run away)</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="K59" s="8" t="inlineStr">
         <is>
           <t>(Fugir)</t>
         </is>
@@ -26217,7 +26217,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>(#tg sorri timidamente e pressiona suavemente os lábios nos seus.)</t>
+          <t>(#tg sorri timidamente e encosta de leve os lábios de #tg_his nos seus.)</t>
         </is>
       </c>
     </row>
@@ -26507,7 +26507,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>(#tg solta uma risada suave e aproxima delicadamente os lábios dos seus.)</t>
+          <t xml:space="preserve">(#tg solta uma risadinha e traz de leve os lábios de #tg_his aos seus.) </t>
         </is>
       </c>
     </row>
@@ -26648,7 +26648,7 @@
       </c>
       <c r="K85" s="8" t="inlineStr">
         <is>
-          <t>O quê?</t>
+          <t>Que?</t>
         </is>
       </c>
       <c r="L85" s="8" t="n"/>
